--- a/artfynd/A 44271-2023 artfynd.xlsx
+++ b/artfynd/A 44271-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44271-2023 artfynd.xlsx
+++ b/artfynd/A 44271-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112630518</v>
+        <v>112630106</v>
       </c>
       <c r="B2" t="n">
-        <v>56768</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Vrm</t>
+          <t>Äskedalen, Äskedalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343371</v>
+        <v>343442</v>
       </c>
       <c r="R2" t="n">
-        <v>6572310</v>
+        <v>6572291</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112631395</v>
+        <v>112632042</v>
       </c>
       <c r="B3" t="n">
-        <v>56768</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,43 +794,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Vrm</t>
+          <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343210</v>
+        <v>343041</v>
       </c>
       <c r="R3" t="n">
-        <v>6572407</v>
+        <v>6572339</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112632042</v>
+        <v>112633682</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,42 +906,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Vrm</t>
+          <t>Vinterstaden, Vinterstaden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343041</v>
+        <v>342740</v>
       </c>
       <c r="R4" t="n">
-        <v>6572339</v>
+        <v>6572024</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +981,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrämde upp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,58 +1013,58 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112633358</v>
+        <v>112630518</v>
       </c>
       <c r="B5" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vinterstaden (Vinterstaden), Vrm</t>
+          <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342763</v>
+        <v>343371</v>
       </c>
       <c r="R5" t="n">
-        <v>6572120</v>
+        <v>6572309</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,54 +1130,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112633394</v>
+        <v>112631395</v>
       </c>
       <c r="B6" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vinterstaden (Vinterstaden), Vrm</t>
+          <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342770</v>
+        <v>343210</v>
       </c>
       <c r="R6" t="n">
-        <v>6572113</v>
+        <v>6572408</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,55 +1243,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112632732</v>
+        <v>112633358</v>
       </c>
       <c r="B7" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vinterstaden (Vinterstaden), Vrm</t>
+          <t>Vinterstaden, Vinterstaden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342796</v>
+        <v>342763</v>
       </c>
       <c r="R7" t="n">
-        <v>6572177</v>
+        <v>6572121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,59 +1355,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112633682</v>
+        <v>112633394</v>
       </c>
       <c r="B8" t="n">
-        <v>55842</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vinterstaden (Vinterstaden), Vrm</t>
+          <t>Vinterstaden, Vinterstaden, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342740</v>
+        <v>342771</v>
       </c>
       <c r="R8" t="n">
-        <v>6572024</v>
+        <v>6572113</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skrämde upp</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,15 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112633673</v>
+        <v>112633462</v>
       </c>
       <c r="B9" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,14 +1495,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vinterstaden (Vinterstaden), Vrm</t>
+          <t>Vinterstaden, Vinterstaden, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342742</v>
+        <v>342790</v>
       </c>
       <c r="R9" t="n">
-        <v>6572022</v>
+        <v>6572118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,15 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112633462</v>
+        <v>112633673</v>
       </c>
       <c r="B10" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,14 +1603,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vinterstaden (Vinterstaden), Vrm</t>
+          <t>Vinterstaden, Vinterstaden, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342790</v>
+        <v>342742</v>
       </c>
       <c r="R10" t="n">
-        <v>6572118</v>
+        <v>6572022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,55 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112631738</v>
+        <v>112633900</v>
       </c>
       <c r="B11" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Vrm</t>
+          <t>Kvarnmyren, Kvarnmyren, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>343124</v>
+        <v>342756</v>
       </c>
       <c r="R11" t="n">
-        <v>6572342</v>
+        <v>6571980</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1760,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,345 +1784,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112633900</v>
-      </c>
-      <c r="B12" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Kvarnmyren (Kvarnmyren), Vrm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>342756</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6571980</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Årjäng</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Sillerud</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112634025</v>
-      </c>
-      <c r="B13" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Kvarnmyren (Kvarnmyren), Vrm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>342758</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6571966</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Årjäng</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Sillerud</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112630106</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91607</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>788</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hydnellum geogenium</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Äskedalen (Äskedalen), Vrm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>343442</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6572291</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Årjäng</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Sillerud</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
